--- a/templates/诈骗预警/scripts.xlsx
+++ b/templates/诈骗预警/scripts.xlsx
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>roboforex_scam_ahmedabad</t>
+          <t>ahmedabad_19lakh_pakistan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Another major forex scam has been exposed, and this time, the fraud is worth over 15 crore rupees. The Ahmedabad Cyber Crime Cell has busted a fake forex trading racket under its Mule Hunt 2.0 operation. Five accused have been arrested for allegedly running fraudulent investment schemes. The gang reportedly lured people with fake RoboForex investment opportunities, promising attractive returns. Instead, victims lost their hard-earned money. So far, investigators have linked the accused to 31 cyber fraud cases, involving a staggering 15.31 crore rupees. Authorities have also seized several mobile phones and important documents as the investigation continues. Before investing with any forex broker, always verify whether it is regulated and check its credibility. Don't fall for guaranteed profits or unrealistic returns. Use WikiFX to verify a brokers license, check real user reviews, and identify potential scam brokers before investing. Stay informed. Stay protected.</t>
+          <t>Another forex investment scam has surfaced in India, and this time, investigators are probing an alleged Pakistan link after one investor lost 19 lakh rupees. Ahmedabad Cyber Crime Police have arrested a 26-year-old man from Bihar in connection with an alleged investment fraud involving the forex and cryptocurrency platform Winprofx. According to police, the victim was attracted through forex trading videos on social media and was promised high returns. He invested nearly 19 lakh rupees in cryptocurrency and US dollar-based trades. Although the platform dashboard showed significant profits, the investor was unable to withdraw any funds. Investigators allege that Winprofx may be linked to a Pakistani citizen and are now tracing the overseas money trail and looking for more possible victims. This case is another reminder that fake investment platforms often display impressive profits but block withdrawals when investors try to access their money. Always verify a platform before investing. Before you trust any forex broker or investment platform, check its regulatory status, licenses, and user reviews on WikiFX. Stay informed. Stay protected.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>forex scam cyber crime police arrest fraud India investigation</t>
+          <t>forex crypto scam police arrest India investigation fraud money</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
